--- a/tests/emissoes_resultantes.xlsx
+++ b/tests/emissoes_resultantes.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2246084946175152</v>
+        <v>0.1866978796637842</v>
       </c>
       <c r="D2" t="n">
-        <v>3.899611088392017e-07</v>
+        <v>4.222244722653409e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.999320059907263e-06</v>
+        <v>4.321826995178448e-06</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.518039834687447</v>
+        <v>2.445735657524616</v>
       </c>
       <c r="D3" t="n">
-        <v>3.649357153566392e-06</v>
+        <v>6.033914585919518e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>3.724078925451225e-05</v>
+        <v>6.160768792097357e-05</v>
       </c>
     </row>
   </sheetData>

--- a/tests/emissoes_resultantes.xlsx
+++ b/tests/emissoes_resultantes.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1866978796637842</v>
+        <v>0.1686353293774712</v>
       </c>
       <c r="D2" t="n">
-        <v>4.222244722653409e-07</v>
+        <v>3.945283294721799e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.321826995178448e-06</v>
+        <v>4.023287125100374e-06</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.445735657524616</v>
+        <v>3.974327839357897</v>
       </c>
       <c r="D3" t="n">
-        <v>6.033914585919518e-06</v>
+        <v>9.940577472604482e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.160768792097357e-05</v>
+        <v>0.0001013259593542056</v>
       </c>
     </row>
   </sheetData>
